--- a/Структура архитектуры проекта.xlsx
+++ b/Структура архитектуры проекта.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\power\source\repos\AsuGenerator.Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EADD1CC-C15A-424D-9294-4D9D1D04AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A36D4B-BC65-4A50-B08B-FB466E7F6D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>Папка</t>
   </si>
@@ -84,34 +84,66 @@
     <t>Атомарный CAD-движок. Графический робот. Загружает подложки рамок А3, чертит провода и расставляет векторные блоки оборудования.</t>
   </si>
   <si>
-    <t>Генератор документов. Программно собирает b2b-спецификацию в Excel по ГОСТу с автоматическим расчетом метража проводов.</t>
-  </si>
-  <si>
     <t>Расчетное инженерное ядро. Калькулятор токов, логика подбора КЭАЗ/ОВЕН/EKF и защита от переполнения каналов I/O.</t>
   </si>
   <si>
     <t>Интеллектуальный парсер. Безопасно считывает заполненные опросные листы Excel через Named Ranges (Именованные ячейки) без привязки к координатам.</t>
   </si>
   <si>
-    <t>Исправить наложения текста автоматов</t>
-  </si>
-  <si>
     <t>Что нужно сделать</t>
   </si>
   <si>
     <t>Исправить логику расчета</t>
+  </si>
+  <si>
+    <t>PriceCalculationService.cs</t>
+  </si>
+  <si>
+    <t>Модуль финансовых расчетов и калькуляции цен</t>
+  </si>
+  <si>
+    <t>Модуль формирования документов для закупщиков и клиентов</t>
+  </si>
+  <si>
+    <t>Program.cs</t>
+  </si>
+  <si>
+    <t>Точка входа приложения (Регистрация Scoped-сервисов и лицензий)</t>
+  </si>
+  <si>
+    <t>Визуальный слой Blazor (UI)</t>
+  </si>
+  <si>
+    <t>Главный экран: загрузка ТЗ, ввод маржи, кнопки генерации</t>
+  </si>
+  <si>
+    <t>Pages</t>
+  </si>
+  <si>
+    <t>Слой b2b бизнес-логики и CAD-инфраструктуры</t>
+  </si>
+  <si>
+    <t>Исправить текст в основной надписи</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -121,6 +153,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -153,10 +193,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -164,13 +205,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -179,8 +220,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -459,11 +510,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="47.88671875" style="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="1"/>
@@ -480,105 +531,155 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="9"/>
+    </row>
+    <row r="3" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>9</v>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{692516A9-0F9D-4108-96CA-550209B8688D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>